--- a/FPS_Test/Assets/Excel/Condition/ConditionData.xlsx
+++ b/FPS_Test/Assets/Excel/Condition/ConditionData.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2024\00 GitHub\Game_Team\Inventory\Assets\Excel\Condition\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2024\GitHub\game_team\FPS_Test\Assets\Excel\Condition\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7F34816-FB04-4C15-90D9-486D076EABAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47D58E73-8203-44D7-83D4-BDC73BA1D41E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5010" yWindow="-13155" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ConditionAbility" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>id</t>
   </si>
@@ -79,6 +79,10 @@
   </si>
   <si>
     <t>Regen</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>None</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -588,7 +592,26 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="7" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+    </row>
     <row r="8" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="9" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="10" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.4"/>
